--- a/CommandList.xlsx
+++ b/CommandList.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyProj\OrchProvider\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E5C7C0-8795-464B-9C55-537013746C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9177C9C1-E9F0-49FE-AE62-2C529C4D9617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16103" yWindow="12615" windowWidth="28995" windowHeight="15675" tabRatio="606" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="606" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="ヘルプ進捗" sheetId="2" r:id="rId2"/>
+    <sheet name="Copy-Itemテスト" sheetId="3" r:id="rId2"/>
+    <sheet name="ヘルプ進捗" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="467">
   <si>
     <t>Command</t>
     <phoneticPr fontId="4"/>
@@ -2669,6 +2670,48 @@
   </si>
   <si>
     <t>Enable-OrchMaintenanceMode.md</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>CopyTo</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>CopyFrom</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>20.10.16</t>
+  </si>
+  <si>
+    <t>21.10.4</t>
+  </si>
+  <si>
+    <t>22.4.4</t>
+  </si>
+  <si>
+    <t>23.10.0</t>
+  </si>
+  <si>
+    <t>23.10.6</t>
+  </si>
+  <si>
+    <t>24.10.0</t>
+  </si>
+  <si>
+    <t>Automation Cloud</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>NA</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>23.4.0 (16.0)</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>22.10.1 (15.0)</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -3031,10 +3074,10 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="9" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="12" borderId="0" xfId="9" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
@@ -3043,10 +3086,10 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3834,7 +3877,7 @@
       </c>
     </row>
     <row r="3" spans="1:18" ht="35.25" x14ac:dyDescent="0.7">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="46" t="s">
         <v>105</v>
       </c>
       <c r="B3" s="12" t="s">
@@ -3877,7 +3920,7 @@
       <c r="R3" s="4"/>
     </row>
     <row r="4" spans="1:18" ht="70.5" x14ac:dyDescent="0.7">
-      <c r="A4" s="42"/>
+      <c r="A4" s="46"/>
       <c r="B4" s="12" t="s">
         <v>75</v>
       </c>
@@ -3918,7 +3961,7 @@
       <c r="R4" s="7"/>
     </row>
     <row r="5" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A5" s="42"/>
+      <c r="A5" s="46"/>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
@@ -3949,7 +3992,7 @@
       <c r="R5" s="4"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A6" s="42"/>
+      <c r="A6" s="46"/>
       <c r="B6" s="12" t="s">
         <v>75</v>
       </c>
@@ -3985,7 +4028,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="52.9" x14ac:dyDescent="0.7">
-      <c r="A7" s="42"/>
+      <c r="A7" s="46"/>
       <c r="B7" s="12" t="s">
         <v>75</v>
       </c>
@@ -4028,7 +4071,7 @@
       <c r="R7" s="10"/>
     </row>
     <row r="8" spans="1:18" ht="52.9" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A8" s="42"/>
+      <c r="A8" s="46"/>
       <c r="B8" s="12" t="s">
         <v>75</v>
       </c>
@@ -4071,7 +4114,7 @@
       <c r="R8" s="17"/>
     </row>
     <row r="9" spans="1:18" ht="52.9" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A9" s="42"/>
+      <c r="A9" s="46"/>
       <c r="B9" s="12" t="s">
         <v>75</v>
       </c>
@@ -4116,7 +4159,7 @@
       </c>
     </row>
     <row r="10" spans="1:18" ht="105.75" x14ac:dyDescent="0.7">
-      <c r="A10" s="42"/>
+      <c r="A10" s="46"/>
       <c r="B10" s="12" t="s">
         <v>75</v>
       </c>
@@ -4161,7 +4204,7 @@
       </c>
     </row>
     <row r="11" spans="1:18" ht="52.9" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A11" s="42"/>
+      <c r="A11" s="46"/>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -4198,7 +4241,7 @@
       </c>
     </row>
     <row r="12" spans="1:18" ht="141" x14ac:dyDescent="0.7">
-      <c r="A12" s="42"/>
+      <c r="A12" s="46"/>
       <c r="B12" s="12" t="s">
         <v>75</v>
       </c>
@@ -4633,7 +4676,7 @@
       </c>
     </row>
     <row r="23" spans="1:18" ht="158.65" x14ac:dyDescent="0.7">
-      <c r="A23" s="46" t="s">
+      <c r="A23" s="43" t="s">
         <v>108</v>
       </c>
       <c r="B23" s="12" t="s">
@@ -4688,7 +4731,7 @@
       <c r="R23" s="10"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A24" s="46"/>
+      <c r="A24" s="43"/>
       <c r="B24" s="12" t="s">
         <v>75</v>
       </c>
@@ -4725,7 +4768,7 @@
       </c>
     </row>
     <row r="25" spans="1:18" ht="211.5" x14ac:dyDescent="0.7">
-      <c r="A25" s="46"/>
+      <c r="A25" s="43"/>
       <c r="B25" s="12" t="s">
         <v>75</v>
       </c>
@@ -4771,7 +4814,7 @@
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A26" s="46"/>
+      <c r="A26" s="43"/>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
@@ -4795,7 +4838,7 @@
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A27" s="46"/>
+      <c r="A27" s="43"/>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
@@ -4816,7 +4859,7 @@
       </c>
     </row>
     <row r="28" spans="1:18" ht="123.4" x14ac:dyDescent="0.7">
-      <c r="A28" s="47" t="s">
+      <c r="A28" s="42" t="s">
         <v>152</v>
       </c>
       <c r="B28" s="12" t="s">
@@ -4867,7 +4910,7 @@
       <c r="R28" s="10"/>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A29" s="47"/>
+      <c r="A29" s="42"/>
       <c r="B29" s="20" t="s">
         <v>151</v>
       </c>
@@ -4900,7 +4943,7 @@
       </c>
     </row>
     <row r="30" spans="1:18" ht="35.25" x14ac:dyDescent="0.7">
-      <c r="A30" s="47"/>
+      <c r="A30" s="42"/>
       <c r="B30" t="s">
         <v>75</v>
       </c>
@@ -4941,7 +4984,7 @@
       <c r="R30" s="10"/>
     </row>
     <row r="31" spans="1:18" ht="35.25" x14ac:dyDescent="0.7">
-      <c r="A31" s="43" t="s">
+      <c r="A31" s="47" t="s">
         <v>109</v>
       </c>
       <c r="B31" s="12" t="s">
@@ -4990,7 +5033,7 @@
       <c r="Q31" s="11"/>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A32" s="43"/>
+      <c r="A32" s="47"/>
       <c r="B32" s="19" t="s">
         <v>210</v>
       </c>
@@ -5019,7 +5062,7 @@
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A33" s="43"/>
+      <c r="A33" s="47"/>
       <c r="B33" s="12" t="s">
         <v>75</v>
       </c>
@@ -5057,7 +5100,7 @@
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A34" s="43"/>
+      <c r="A34" s="47"/>
       <c r="B34" s="39" t="s">
         <v>246</v>
       </c>
@@ -5095,7 +5138,7 @@
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A35" s="43"/>
+      <c r="A35" s="47"/>
       <c r="B35" s="12" t="s">
         <v>75</v>
       </c>
@@ -5135,7 +5178,7 @@
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A36" s="43"/>
+      <c r="A36" s="47"/>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
@@ -5224,7 +5267,7 @@
       </c>
     </row>
     <row r="39" spans="1:18" ht="52.9" x14ac:dyDescent="0.7">
-      <c r="A39" s="42" t="s">
+      <c r="A39" s="46" t="s">
         <v>110</v>
       </c>
       <c r="B39" s="12" t="s">
@@ -5275,7 +5318,7 @@
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A40" s="42"/>
+      <c r="A40" s="46"/>
       <c r="B40" s="12" t="s">
         <v>75</v>
       </c>
@@ -5318,7 +5361,7 @@
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A41" s="42"/>
+      <c r="A41" s="46"/>
       <c r="B41" s="12" t="s">
         <v>75</v>
       </c>
@@ -5358,7 +5401,7 @@
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A42" s="42"/>
+      <c r="A42" s="46"/>
       <c r="B42" s="12" t="s">
         <v>75</v>
       </c>
@@ -5403,7 +5446,7 @@
       <c r="R42" s="4"/>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A43" s="42"/>
+      <c r="A43" s="46"/>
       <c r="B43" s="12"/>
       <c r="C43" s="12"/>
       <c r="D43" s="12"/>
@@ -5424,7 +5467,7 @@
       </c>
     </row>
     <row r="44" spans="1:18" ht="211.5" x14ac:dyDescent="0.7">
-      <c r="A44" s="46" t="s">
+      <c r="A44" s="43" t="s">
         <v>131</v>
       </c>
       <c r="B44" s="12" t="s">
@@ -5473,7 +5516,7 @@
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A45" s="46"/>
+      <c r="A45" s="43"/>
       <c r="B45" s="12" t="s">
         <v>75</v>
       </c>
@@ -5513,7 +5556,7 @@
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A46" s="46"/>
+      <c r="A46" s="43"/>
       <c r="B46" s="28" t="s">
         <v>75</v>
       </c>
@@ -6038,7 +6081,7 @@
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A60" s="46" t="s">
+      <c r="A60" s="43" t="s">
         <v>113</v>
       </c>
       <c r="B60" s="12" t="s">
@@ -6087,7 +6130,7 @@
       <c r="R60" s="10"/>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A61" s="46"/>
+      <c r="A61" s="43"/>
       <c r="B61" s="12" t="s">
         <v>75</v>
       </c>
@@ -6131,7 +6174,7 @@
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A62" s="46"/>
+      <c r="A62" s="43"/>
       <c r="B62" s="12" t="s">
         <v>75</v>
       </c>
@@ -6174,7 +6217,7 @@
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A63" s="46"/>
+      <c r="A63" s="43"/>
       <c r="B63" s="19" t="s">
         <v>176</v>
       </c>
@@ -6200,7 +6243,7 @@
       </c>
     </row>
     <row r="64" spans="1:18" ht="52.9" x14ac:dyDescent="0.7">
-      <c r="A64" s="47" t="s">
+      <c r="A64" s="42" t="s">
         <v>114</v>
       </c>
       <c r="B64" s="12" t="s">
@@ -6251,7 +6294,7 @@
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A65" s="47"/>
+      <c r="A65" s="42"/>
       <c r="B65" s="21" t="s">
         <v>75</v>
       </c>
@@ -6300,7 +6343,7 @@
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A66" s="47"/>
+      <c r="A66" s="42"/>
       <c r="B66" s="12" t="s">
         <v>75</v>
       </c>
@@ -6342,7 +6385,7 @@
       <c r="R66" s="17"/>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A67" s="47"/>
+      <c r="A67" s="42"/>
       <c r="B67" s="12"/>
       <c r="C67" s="12"/>
       <c r="D67" s="12"/>
@@ -6366,7 +6409,7 @@
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A68" s="47"/>
+      <c r="A68" s="42"/>
       <c r="B68" t="s">
         <v>75</v>
       </c>
@@ -6406,7 +6449,7 @@
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A69" s="46" t="s">
+      <c r="A69" s="43" t="s">
         <v>193</v>
       </c>
       <c r="B69" s="12" t="s">
@@ -6451,7 +6494,7 @@
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A70" s="46"/>
+      <c r="A70" s="43"/>
       <c r="B70" s="12" t="s">
         <v>75</v>
       </c>
@@ -6494,7 +6537,7 @@
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A71" s="42" t="s">
+      <c r="A71" s="46" t="s">
         <v>130</v>
       </c>
       <c r="B71" s="12" t="s">
@@ -6536,7 +6579,7 @@
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A72" s="42"/>
+      <c r="A72" s="46"/>
       <c r="B72" s="12" t="s">
         <v>75</v>
       </c>
@@ -6574,7 +6617,7 @@
       </c>
     </row>
     <row r="73" spans="1:18" ht="52.9" x14ac:dyDescent="0.7">
-      <c r="A73" s="42"/>
+      <c r="A73" s="46"/>
       <c r="B73" s="12" t="s">
         <v>75</v>
       </c>
@@ -6617,7 +6660,7 @@
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A74" s="42"/>
+      <c r="A74" s="46"/>
       <c r="B74" s="12"/>
       <c r="C74" s="12"/>
       <c r="D74" s="12"/>
@@ -6638,7 +6681,7 @@
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A75" s="42"/>
+      <c r="A75" s="46"/>
       <c r="B75" s="20" t="s">
         <v>151</v>
       </c>
@@ -6671,7 +6714,7 @@
       <c r="R75" s="21"/>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A76" s="42"/>
+      <c r="A76" s="46"/>
       <c r="B76" s="20"/>
       <c r="C76" s="20"/>
       <c r="D76" s="20"/>
@@ -6698,7 +6741,7 @@
       <c r="R76" s="21"/>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A77" s="42"/>
+      <c r="A77" s="46"/>
       <c r="B77" s="20"/>
       <c r="C77" s="20"/>
       <c r="D77" s="20"/>
@@ -6725,7 +6768,7 @@
       <c r="R77" s="23"/>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A78" s="42"/>
+      <c r="A78" s="46"/>
       <c r="B78" s="10" t="s">
         <v>202</v>
       </c>
@@ -7064,7 +7107,7 @@
       </c>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A88" s="46" t="s">
+      <c r="A88" s="43" t="s">
         <v>228</v>
       </c>
       <c r="B88" s="27"/>
@@ -7084,7 +7127,7 @@
       </c>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A89" s="46"/>
+      <c r="A89" s="43"/>
       <c r="B89" s="27"/>
       <c r="C89" s="12"/>
       <c r="D89" s="12"/>
@@ -7102,7 +7145,7 @@
       </c>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A90" s="43" t="s">
+      <c r="A90" s="47" t="s">
         <v>232</v>
       </c>
       <c r="B90" s="27"/>
@@ -7122,7 +7165,7 @@
       </c>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.7">
-      <c r="A91" s="43"/>
+      <c r="A91" s="47"/>
       <c r="B91" s="27"/>
       <c r="C91" s="12"/>
       <c r="D91" s="12"/>
@@ -7264,6 +7307,11 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A3:A12"/>
+    <mergeCell ref="A31:A36"/>
+    <mergeCell ref="A18:A22"/>
+    <mergeCell ref="A13:A17"/>
+    <mergeCell ref="A23:A27"/>
     <mergeCell ref="A64:A68"/>
     <mergeCell ref="A69:A70"/>
     <mergeCell ref="A79:A83"/>
@@ -7279,11 +7327,6 @@
     <mergeCell ref="A84:A86"/>
     <mergeCell ref="A47:A54"/>
     <mergeCell ref="A39:A43"/>
-    <mergeCell ref="A3:A12"/>
-    <mergeCell ref="A31:A36"/>
-    <mergeCell ref="A18:A22"/>
-    <mergeCell ref="A13:A17"/>
-    <mergeCell ref="A23:A27"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <conditionalFormatting sqref="B3:I96">
@@ -7312,6 +7355,147 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94C427FE-4FBE-4E72-B82C-3613844698B3}">
+  <dimension ref="A2:K11"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
+  <cols>
+    <col min="1" max="1" width="14.3125" customWidth="1"/>
+    <col min="2" max="2" width="15.625" customWidth="1"/>
+    <col min="6" max="6" width="12.3125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.7">
+      <c r="B2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C2" t="s">
+        <v>457</v>
+      </c>
+      <c r="D2" t="s">
+        <v>458</v>
+      </c>
+      <c r="E2" t="s">
+        <v>459</v>
+      </c>
+      <c r="F2" t="s">
+        <v>466</v>
+      </c>
+      <c r="G2" t="s">
+        <v>460</v>
+      </c>
+      <c r="H2" t="s">
+        <v>465</v>
+      </c>
+      <c r="I2" t="s">
+        <v>461</v>
+      </c>
+      <c r="J2" t="s">
+        <v>462</v>
+      </c>
+      <c r="K2" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.7">
+      <c r="A3" t="s">
+        <v>456</v>
+      </c>
+      <c r="B3" t="s">
+        <v>457</v>
+      </c>
+      <c r="C3" t="s">
+        <v>464</v>
+      </c>
+      <c r="K3" s="41"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.7">
+      <c r="B4" t="s">
+        <v>458</v>
+      </c>
+      <c r="D4" t="s">
+        <v>464</v>
+      </c>
+      <c r="K4" s="41"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.7">
+      <c r="B5" t="s">
+        <v>459</v>
+      </c>
+      <c r="E5" t="s">
+        <v>464</v>
+      </c>
+      <c r="K5" s="41"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.7">
+      <c r="B6" s="41" t="s">
+        <v>466</v>
+      </c>
+      <c r="F6" t="s">
+        <v>464</v>
+      </c>
+      <c r="K6" s="41"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.7">
+      <c r="B7" t="s">
+        <v>460</v>
+      </c>
+      <c r="G7" t="s">
+        <v>464</v>
+      </c>
+      <c r="K7" s="41"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.7">
+      <c r="B8" s="41" t="s">
+        <v>465</v>
+      </c>
+      <c r="H8" t="s">
+        <v>464</v>
+      </c>
+      <c r="K8" s="41"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.7">
+      <c r="B9" t="s">
+        <v>461</v>
+      </c>
+      <c r="I9" t="s">
+        <v>464</v>
+      </c>
+      <c r="K9" s="41"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.7">
+      <c r="B10" t="s">
+        <v>462</v>
+      </c>
+      <c r="J10" t="s">
+        <v>464</v>
+      </c>
+      <c r="K10" s="41"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.7">
+      <c r="B11" t="s">
+        <v>463</v>
+      </c>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="41"/>
+      <c r="J11" s="41"/>
+      <c r="K11" t="s">
+        <v>464</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37B91805-B5B4-49AB-9E11-D058FB1F0566}">
   <dimension ref="A1:H166"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>

--- a/CommandList.xlsx
+++ b/CommandList.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyProj\OrchProvider\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9177C9C1-E9F0-49FE-AE62-2C529C4D9617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0F88B67-7A86-4DDA-B3BA-9C6CB5EC3463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="606" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-130" yWindow="-130" windowWidth="19460" windowHeight="11540" tabRatio="606" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Copy-Itemテスト" sheetId="3" r:id="rId2"/>
-    <sheet name="ヘルプ進捗" sheetId="2" r:id="rId3"/>
+    <sheet name="Newに改名" sheetId="4" r:id="rId2"/>
+    <sheet name="Copy-Itemテスト" sheetId="3" r:id="rId3"/>
+    <sheet name="ヘルプ進捗" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="484">
   <si>
     <t>Command</t>
     <phoneticPr fontId="4"/>
@@ -2712,6 +2713,76 @@
   </si>
   <si>
     <t>22.10.1 (15.0)</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>cmdlets</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Add-OrchPmUserBulk</t>
+  </si>
+  <si>
+    <t>Add-OrchProcess</t>
+  </si>
+  <si>
+    <t>Add-OrchTrigger</t>
+  </si>
+  <si>
+    <t>Add-OrchBucket</t>
+  </si>
+  <si>
+    <t>.cs に埋めた verb</t>
+    <rPh sb="5" eb="6">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>.psd1</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>.cs のファイル名</t>
+    <rPh sb="9" eb="10">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>jp pdf</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>us pdf</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>jp help filename</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>jp help contents</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>us help filename</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>us help contents</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Add-OrchPmGroup</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Add-OrchMachine</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Add-OrchQueue</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -3901,7 +3972,7 @@
         <v>30</v>
       </c>
       <c r="L3" s="5" t="str">
-        <f>J3 &amp; "-" &amp; K3</f>
+        <f t="shared" ref="L3:L12" si="0">J3 &amp; "-" &amp; K3</f>
         <v>Set-Location</v>
       </c>
       <c r="M3" s="5" t="s">
@@ -3942,7 +4013,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="8" t="str">
-        <f t="shared" ref="L4" si="0">J4 &amp; "-" &amp; K4</f>
+        <f t="shared" si="0"/>
         <v>Get-ChildItem</v>
       </c>
       <c r="M4" s="8" t="s">
@@ -3977,7 +4048,7 @@
         <v>5</v>
       </c>
       <c r="L5" s="18" t="str">
-        <f>J5 &amp; "-" &amp; K5</f>
+        <f t="shared" si="0"/>
         <v>Copy-Item</v>
       </c>
       <c r="M5" s="4"/>
@@ -4014,7 +4085,7 @@
         <v>5</v>
       </c>
       <c r="L6" s="10" t="str">
-        <f t="shared" ref="L6:L66" si="1">J6 &amp; "-" &amp; K6</f>
+        <f t="shared" si="0"/>
         <v>Get-Item</v>
       </c>
       <c r="N6" t="s">
@@ -4050,7 +4121,7 @@
         <v>5</v>
       </c>
       <c r="L7" s="10" t="str">
-        <f>J7 &amp; "-" &amp; K7</f>
+        <f t="shared" si="0"/>
         <v>Invoke-Item</v>
       </c>
       <c r="M7" s="10" t="s">
@@ -4093,7 +4164,7 @@
         <v>5</v>
       </c>
       <c r="L8" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>New-Item</v>
       </c>
       <c r="M8" s="10" t="s">
@@ -4136,7 +4207,7 @@
         <v>5</v>
       </c>
       <c r="L9" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Move-Item</v>
       </c>
       <c r="M9" s="10" t="s">
@@ -4181,7 +4252,7 @@
         <v>5</v>
       </c>
       <c r="L10" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Rename-Item</v>
       </c>
       <c r="M10" s="10" t="s">
@@ -4220,7 +4291,7 @@
         <v>5</v>
       </c>
       <c r="L11" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Set-Item</v>
       </c>
       <c r="M11" s="10"/>
@@ -4263,7 +4334,7 @@
         <v>5</v>
       </c>
       <c r="L12" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Remove-Item</v>
       </c>
       <c r="M12" s="10" t="s">
@@ -4317,7 +4388,7 @@
         <v>97</v>
       </c>
       <c r="L13" s="10" t="str">
-        <f t="shared" ref="L13:L22" si="2">J13 &amp; "-" &amp; K13</f>
+        <f t="shared" ref="L13:L22" si="1">J13 &amp; "-" &amp; K13</f>
         <v>Get-OrchLibrary</v>
       </c>
       <c r="N13" t="s">
@@ -4453,7 +4524,7 @@
         <v>97</v>
       </c>
       <c r="L16" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>Import-OrchLibrary</v>
       </c>
       <c r="N16" s="11" t="s">
@@ -4485,7 +4556,7 @@
         <v>97</v>
       </c>
       <c r="L17" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>Export-OrchLibrary</v>
       </c>
       <c r="N17" s="11" t="s">
@@ -4531,7 +4602,7 @@
         <v>96</v>
       </c>
       <c r="L18" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>Get-OrchPackage</v>
       </c>
       <c r="N18" t="s">
@@ -4636,7 +4707,7 @@
         <v>96</v>
       </c>
       <c r="L21" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>Import-OrchPackage</v>
       </c>
       <c r="N21" s="11" t="s">
@@ -4665,7 +4736,7 @@
         <v>96</v>
       </c>
       <c r="L22" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>Export-OrchPackage</v>
       </c>
       <c r="N22" s="11" t="s">
@@ -4710,7 +4781,7 @@
         <v>39</v>
       </c>
       <c r="L23" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="L23:L54" si="2">J23 &amp; "-" &amp; K23</f>
         <v>Get-OrchJob</v>
       </c>
       <c r="M23" s="10" t="s">
@@ -4757,7 +4828,7 @@
         <v>39</v>
       </c>
       <c r="L24" s="10" t="str">
-        <f>J24 &amp; "-" &amp; K24</f>
+        <f t="shared" si="2"/>
         <v>Start-OrchJob</v>
       </c>
       <c r="M24" s="10" t="s">
@@ -4794,7 +4865,7 @@
         <v>39</v>
       </c>
       <c r="L25" s="10" t="str">
-        <f>J25 &amp; "-" &amp; K25</f>
+        <f t="shared" si="2"/>
         <v>Stop-OrchJob</v>
       </c>
       <c r="M25" s="10" t="s">
@@ -4830,7 +4901,7 @@
         <v>39</v>
       </c>
       <c r="L26" s="10" t="str">
-        <f>J26 &amp; "-" &amp; K26</f>
+        <f t="shared" si="2"/>
         <v>Open-OrchJob</v>
       </c>
       <c r="N26" t="s">
@@ -4854,7 +4925,7 @@
         <v>231</v>
       </c>
       <c r="L27" s="10" t="str">
-        <f>J27 &amp; "-" &amp; K27</f>
+        <f t="shared" si="2"/>
         <v>Get-OrchJobStats</v>
       </c>
     </row>
@@ -4889,7 +4960,7 @@
         <v>153</v>
       </c>
       <c r="L28" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Get-OrchLog</v>
       </c>
       <c r="M28" s="10" t="s">
@@ -4928,7 +4999,7 @@
         <v>154</v>
       </c>
       <c r="L29" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Get-OrchLogByHost</v>
       </c>
       <c r="M29" s="21"/>
@@ -4972,7 +5043,7 @@
         <v>204</v>
       </c>
       <c r="L30" s="10" t="str">
-        <f>J30 &amp; "-" &amp; K30</f>
+        <f t="shared" si="2"/>
         <v>Get-OrchAuditLog</v>
       </c>
       <c r="O30" s="11" t="s">
@@ -5018,7 +5089,7 @@
         <v>51</v>
       </c>
       <c r="L31" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Get-OrchProcess</v>
       </c>
       <c r="N31" t="s">
@@ -5051,7 +5122,7 @@
         <v>51</v>
       </c>
       <c r="L32" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Add-OrchProcess</v>
       </c>
       <c r="N32" t="s">
@@ -5092,7 +5163,7 @@
         <v>51</v>
       </c>
       <c r="L33" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Remove-OrchProcess</v>
       </c>
       <c r="N33" t="s">
@@ -5130,7 +5201,7 @@
         <v>206</v>
       </c>
       <c r="L34" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Update-OrchProcessVersion</v>
       </c>
       <c r="N34" s="11" t="s">
@@ -5170,7 +5241,7 @@
         <v>206</v>
       </c>
       <c r="L35" s="10" t="str">
-        <f>J35 &amp; "-" &amp; K35</f>
+        <f t="shared" si="2"/>
         <v>Reset-OrchProcessVersion</v>
       </c>
       <c r="N35" s="11" t="s">
@@ -5194,7 +5265,7 @@
         <v>51</v>
       </c>
       <c r="L36" s="17" t="str">
-        <f>J36 &amp; "-" &amp; K36</f>
+        <f t="shared" si="2"/>
         <v>Copy-OrchProcess</v>
       </c>
       <c r="N36" t="s">
@@ -5239,7 +5310,7 @@
         <v>227</v>
       </c>
       <c r="L37" s="10" t="str">
-        <f>J37 &amp; "-" &amp; K37</f>
+        <f t="shared" si="2"/>
         <v>Get-OrchRobot</v>
       </c>
     </row>
@@ -5262,7 +5333,7 @@
         <v>227</v>
       </c>
       <c r="L38" s="10" t="str">
-        <f>J38 &amp; "-" &amp; K38</f>
+        <f t="shared" si="2"/>
         <v>Remove-OrchRobot</v>
       </c>
     </row>
@@ -5301,7 +5372,7 @@
         <v>58</v>
       </c>
       <c r="L39" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Get-OrchUser</v>
       </c>
       <c r="N39" t="s">
@@ -5350,7 +5421,7 @@
         <v>58</v>
       </c>
       <c r="L40" s="10" t="str">
-        <f>J40 &amp; "-" &amp; K40</f>
+        <f t="shared" si="2"/>
         <v>Remove-OrchUser</v>
       </c>
       <c r="N40" t="s">
@@ -5393,7 +5464,7 @@
         <v>274</v>
       </c>
       <c r="L41" s="10" t="str">
-        <f>J41 &amp; "-" &amp; K41</f>
+        <f t="shared" si="2"/>
         <v>Get-OrchCurrentUser</v>
       </c>
       <c r="N41" t="s">
@@ -5433,7 +5504,7 @@
         <v>275</v>
       </c>
       <c r="L42" s="10" t="str">
-        <f>J42 &amp; "-" &amp; K42</f>
+        <f t="shared" si="2"/>
         <v>Update-OrchCurrentUserURPassword</v>
       </c>
       <c r="M42" s="4"/>
@@ -5462,7 +5533,7 @@
         <v>58</v>
       </c>
       <c r="L43" s="10" t="str">
-        <f>J43 &amp; "-" &amp; K43</f>
+        <f t="shared" si="2"/>
         <v>Import-OrchUser</v>
       </c>
     </row>
@@ -5499,7 +5570,7 @@
         <v>59</v>
       </c>
       <c r="L44" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Get-OrchRole</v>
       </c>
       <c r="N44" t="s">
@@ -5548,7 +5619,7 @@
         <v>59</v>
       </c>
       <c r="L45" s="10" t="str">
-        <f>J45 &amp; "-" &amp; K45</f>
+        <f t="shared" si="2"/>
         <v>Remove-OrchRole</v>
       </c>
       <c r="N45" t="s">
@@ -5588,7 +5659,7 @@
         <v>59</v>
       </c>
       <c r="L46" s="10" t="str">
-        <f>J46 &amp; "-" &amp; K46</f>
+        <f t="shared" si="2"/>
         <v>Copy-OrchRole</v>
       </c>
       <c r="N46" s="11" t="s">
@@ -5631,7 +5702,7 @@
         <v>62</v>
       </c>
       <c r="L47" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Get-OrchFolderUser</v>
       </c>
       <c r="N47" s="11" t="s">
@@ -5676,7 +5747,7 @@
         <v>62</v>
       </c>
       <c r="L48" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Add-OrchFolderUser</v>
       </c>
       <c r="N48" s="11" t="s">
@@ -5718,7 +5789,7 @@
         <v>62</v>
       </c>
       <c r="L49" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Remove-OrchFolderUser</v>
       </c>
       <c r="N49" s="11" t="s">
@@ -5750,7 +5821,7 @@
         <v>62</v>
       </c>
       <c r="L50" s="17" t="str">
-        <f>J50 &amp; "-" &amp; K50</f>
+        <f t="shared" si="2"/>
         <v>Copy-OrchFolderUser</v>
       </c>
       <c r="O50" t="s">
@@ -5774,7 +5845,7 @@
         <v>245</v>
       </c>
       <c r="L51" s="10" t="str">
-        <f>J51 &amp; "-" &amp; K51</f>
+        <f t="shared" si="2"/>
         <v>Enable-OrchFolderUserAlert</v>
       </c>
     </row>
@@ -5795,7 +5866,7 @@
         <v>245</v>
       </c>
       <c r="L52" s="10" t="str">
-        <f>J52 &amp; "-" &amp; K52</f>
+        <f t="shared" si="2"/>
         <v>Disable-OrchFolderUserAlert</v>
       </c>
     </row>
@@ -5828,7 +5899,7 @@
         <v>156</v>
       </c>
       <c r="L53" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Add-OrchRoleToFolderUser</v>
       </c>
       <c r="N53" s="11" t="s">
@@ -5872,7 +5943,7 @@
         <v>157</v>
       </c>
       <c r="L54" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Remove-OrchRoleFromFolderUser</v>
       </c>
       <c r="N54" s="11" t="s">
@@ -5917,7 +5988,7 @@
         <v>79</v>
       </c>
       <c r="L55" s="10" t="str">
-        <f>J55 &amp; "-" &amp; K55</f>
+        <f t="shared" ref="L55:L78" si="3">J55 &amp; "-" &amp; K55</f>
         <v>Get-OrchMachine</v>
       </c>
       <c r="N55" t="s">
@@ -5949,7 +6020,7 @@
         <v>79</v>
       </c>
       <c r="L56" s="21" t="str">
-        <f>J56 &amp; "-" &amp; K56</f>
+        <f t="shared" si="3"/>
         <v>Add-OrchMachine</v>
       </c>
       <c r="M56" s="21"/>
@@ -5980,7 +6051,7 @@
         <v>79</v>
       </c>
       <c r="L57" s="21" t="str">
-        <f>J57 &amp; "-" &amp; K57</f>
+        <f t="shared" si="3"/>
         <v>Edit-OrchMachine</v>
       </c>
       <c r="M57" s="21"/>
@@ -6025,7 +6096,7 @@
         <v>79</v>
       </c>
       <c r="L58" s="10" t="str">
-        <f>J58 &amp; "-" &amp; K58</f>
+        <f t="shared" si="3"/>
         <v>Remove-OrchMachine</v>
       </c>
       <c r="N58" t="s">
@@ -6073,7 +6144,7 @@
         <v>79</v>
       </c>
       <c r="L59" s="29" t="str">
-        <f>J59 &amp; "-" &amp; K59</f>
+        <f t="shared" si="3"/>
         <v>Copy-OrchMachine</v>
       </c>
       <c r="O59" t="s">
@@ -6115,7 +6186,7 @@
         <v>67</v>
       </c>
       <c r="L60" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Get-OrchFolderMachine</v>
       </c>
       <c r="N60" t="s">
@@ -6160,7 +6231,7 @@
         <v>67</v>
       </c>
       <c r="L61" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Add-OrchFolderMachine</v>
       </c>
       <c r="N61" t="s">
@@ -6206,7 +6277,7 @@
         <v>67</v>
       </c>
       <c r="L62" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Remove-OrchFolderMachine</v>
       </c>
       <c r="N62" t="s">
@@ -6235,7 +6306,7 @@
         <v>67</v>
       </c>
       <c r="L63" s="17" t="str">
-        <f>J63 &amp; "-" &amp; K63</f>
+        <f t="shared" si="3"/>
         <v>Copy-OrchFolderMachine</v>
       </c>
       <c r="O63" t="s">
@@ -6277,7 +6348,7 @@
         <v>70</v>
       </c>
       <c r="L64" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Set-OrchAsset</v>
       </c>
       <c r="N64" t="s">
@@ -6326,7 +6397,7 @@
         <v>70</v>
       </c>
       <c r="L65" s="10" t="str">
-        <f t="shared" ref="L65" si="3">J65 &amp; "-" &amp; K65</f>
+        <f t="shared" si="3"/>
         <v>Get-OrchAsset</v>
       </c>
       <c r="N65" t="s">
@@ -6373,7 +6444,7 @@
         <v>70</v>
       </c>
       <c r="L66" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Remove-OrchAsset</v>
       </c>
       <c r="N66" t="s">
@@ -6401,7 +6472,7 @@
         <v>70</v>
       </c>
       <c r="L67" s="17" t="str">
-        <f t="shared" ref="L67:L68" si="4">J67 &amp; "-" &amp; K67</f>
+        <f t="shared" si="3"/>
         <v>Copy-OrchAsset</v>
       </c>
       <c r="N67" t="s">
@@ -6438,7 +6509,7 @@
         <v>73</v>
       </c>
       <c r="L68" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>Set-OrchCredentialAsset</v>
       </c>
       <c r="N68" t="s">
@@ -6483,7 +6554,7 @@
         <v>194</v>
       </c>
       <c r="L69" s="10" t="str">
-        <f>J69 &amp; "-" &amp; K69</f>
+        <f t="shared" si="3"/>
         <v>Get-OrchCredentialStore</v>
       </c>
       <c r="N69" t="s">
@@ -6526,7 +6597,7 @@
         <v>194</v>
       </c>
       <c r="L70" s="10" t="str">
-        <f>J70 &amp; "-" &amp; K70</f>
+        <f t="shared" si="3"/>
         <v>Remove-OrchCredentialStore</v>
       </c>
       <c r="N70" t="s">
@@ -6571,7 +6642,7 @@
         <v>126</v>
       </c>
       <c r="L71" s="10" t="str">
-        <f t="shared" ref="L71:L96" si="5">J71 &amp; "-" &amp; K71</f>
+        <f t="shared" si="3"/>
         <v>Get-OrchQueue</v>
       </c>
       <c r="N71" t="s">
@@ -6609,7 +6680,7 @@
         <v>126</v>
       </c>
       <c r="L72" s="10" t="str">
-        <f>J72 &amp; "-" &amp; K72</f>
+        <f t="shared" si="3"/>
         <v>Remove-OrchQueue</v>
       </c>
       <c r="N72" t="s">
@@ -6649,7 +6720,7 @@
         <v>155</v>
       </c>
       <c r="L73" s="10" t="str">
-        <f>J73 &amp; "-" &amp; K73</f>
+        <f t="shared" si="3"/>
         <v>Get-OrchQueueItem</v>
       </c>
       <c r="N73" t="s">
@@ -6676,7 +6747,7 @@
         <v>155</v>
       </c>
       <c r="L74" s="10" t="str">
-        <f>J74 &amp; "-" &amp; K74</f>
+        <f t="shared" si="3"/>
         <v>Export-OrchQueueItem</v>
       </c>
     </row>
@@ -6699,7 +6770,7 @@
         <v>155</v>
       </c>
       <c r="L75" s="21" t="str">
-        <f>J75 &amp; "-" &amp; K75</f>
+        <f t="shared" si="3"/>
         <v>Remove-OrchQueueItem</v>
       </c>
       <c r="M75" s="21"/>
@@ -6730,7 +6801,7 @@
         <v>234</v>
       </c>
       <c r="L76" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>Add-OrchQueueLink</v>
       </c>
       <c r="M76" s="21"/>
@@ -6757,7 +6828,7 @@
         <v>234</v>
       </c>
       <c r="L77" s="21" t="str">
-        <f>J77 &amp; "-" &amp; K77</f>
+        <f t="shared" si="3"/>
         <v>Remove-OrchQueueLink</v>
       </c>
       <c r="M77" s="23"/>
@@ -6779,7 +6850,7 @@
         <v>127</v>
       </c>
       <c r="L78" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>Import-OrchQueueCsv</v>
       </c>
     </row>
@@ -6815,7 +6886,7 @@
         <v>214</v>
       </c>
       <c r="L79" s="10" t="str">
-        <f t="shared" ref="L79:L91" si="6">J79 &amp; "-" &amp; K79</f>
+        <f t="shared" ref="L79:L91" si="4">J79 &amp; "-" &amp; K79</f>
         <v>Get-OrchTrigger</v>
       </c>
     </row>
@@ -6849,7 +6920,7 @@
         <v>214</v>
       </c>
       <c r="L80" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>Remove-OrchTrigger</v>
       </c>
     </row>
@@ -6907,7 +6978,7 @@
         <v>214</v>
       </c>
       <c r="L82" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>Enable-OrchTrigger</v>
       </c>
     </row>
@@ -6941,7 +7012,7 @@
         <v>214</v>
       </c>
       <c r="L83" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>Disable-OrchTrigger</v>
       </c>
     </row>
@@ -7122,7 +7193,7 @@
         <v>229</v>
       </c>
       <c r="L88" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>Get-OrchSession</v>
       </c>
     </row>
@@ -7140,7 +7211,7 @@
         <v>230</v>
       </c>
       <c r="L89" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>Get-OrchSessionStats</v>
       </c>
     </row>
@@ -7160,7 +7231,7 @@
         <v>233</v>
       </c>
       <c r="L90" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>Get-OrchWebHook</v>
       </c>
     </row>
@@ -7178,7 +7249,7 @@
         <v>233</v>
       </c>
       <c r="L91" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>Remove-OrchWebHook</v>
       </c>
     </row>
@@ -7213,7 +7284,7 @@
         <v>143</v>
       </c>
       <c r="L92" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f>J92 &amp; "-" &amp; K92</f>
         <v>Clear-OrchCache</v>
       </c>
       <c r="N92" t="s">
@@ -7250,7 +7321,7 @@
         <v>145</v>
       </c>
       <c r="L93" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f>J93 &amp; "-" &amp; K93</f>
         <v>Edit-OrchConfig</v>
       </c>
       <c r="N93" s="11" t="s">
@@ -7272,7 +7343,7 @@
         <v>148</v>
       </c>
       <c r="L94" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f>J94 &amp; "-" &amp; K94</f>
         <v>Get-OrchIdentityUser</v>
       </c>
     </row>
@@ -7291,7 +7362,7 @@
         <v>150</v>
       </c>
       <c r="L95" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f>J95 &amp; "-" &amp; K95</f>
         <v>Get-OrchIdentityGroup</v>
       </c>
     </row>
@@ -7301,7 +7372,7 @@
       <c r="D96" s="12"/>
       <c r="E96" s="12"/>
       <c r="L96" t="str">
-        <f t="shared" si="5"/>
+        <f>J96 &amp; "-" &amp; K96</f>
         <v>-</v>
       </c>
     </row>
@@ -7355,6 +7426,238 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8BBFCBD-85BC-458D-840F-2B5FC6B61B4B}">
+  <dimension ref="B2:K9"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
+  <cols>
+    <col min="2" max="2" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5" customWidth="1"/>
+    <col min="6" max="7" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.1875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.7">
+      <c r="B2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C2" t="s">
+        <v>472</v>
+      </c>
+      <c r="D2" t="s">
+        <v>474</v>
+      </c>
+      <c r="E2" t="s">
+        <v>473</v>
+      </c>
+      <c r="F2" t="s">
+        <v>477</v>
+      </c>
+      <c r="G2" t="s">
+        <v>478</v>
+      </c>
+      <c r="H2" t="s">
+        <v>479</v>
+      </c>
+      <c r="I2" t="s">
+        <v>480</v>
+      </c>
+      <c r="J2" t="s">
+        <v>475</v>
+      </c>
+      <c r="K2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.7">
+      <c r="B3" t="s">
+        <v>468</v>
+      </c>
+      <c r="C3" t="s">
+        <v>440</v>
+      </c>
+      <c r="D3" t="s">
+        <v>440</v>
+      </c>
+      <c r="E3" t="s">
+        <v>440</v>
+      </c>
+      <c r="F3" t="s">
+        <v>440</v>
+      </c>
+      <c r="G3" t="s">
+        <v>440</v>
+      </c>
+      <c r="H3" t="s">
+        <v>440</v>
+      </c>
+      <c r="I3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.7">
+      <c r="B4" t="s">
+        <v>481</v>
+      </c>
+      <c r="C4" t="s">
+        <v>440</v>
+      </c>
+      <c r="D4" t="s">
+        <v>440</v>
+      </c>
+      <c r="E4" t="s">
+        <v>440</v>
+      </c>
+      <c r="F4" t="s">
+        <v>440</v>
+      </c>
+      <c r="G4" t="s">
+        <v>440</v>
+      </c>
+      <c r="H4" t="s">
+        <v>440</v>
+      </c>
+      <c r="I4" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.7">
+      <c r="B5" t="s">
+        <v>482</v>
+      </c>
+      <c r="C5" t="s">
+        <v>440</v>
+      </c>
+      <c r="D5" t="s">
+        <v>440</v>
+      </c>
+      <c r="E5" t="s">
+        <v>440</v>
+      </c>
+      <c r="F5" t="s">
+        <v>440</v>
+      </c>
+      <c r="G5" t="s">
+        <v>440</v>
+      </c>
+      <c r="H5" t="s">
+        <v>440</v>
+      </c>
+      <c r="I5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.7">
+      <c r="B6" t="s">
+        <v>469</v>
+      </c>
+      <c r="C6" t="s">
+        <v>440</v>
+      </c>
+      <c r="D6" t="s">
+        <v>440</v>
+      </c>
+      <c r="E6" t="s">
+        <v>440</v>
+      </c>
+      <c r="F6" t="s">
+        <v>440</v>
+      </c>
+      <c r="G6" t="s">
+        <v>440</v>
+      </c>
+      <c r="H6" t="s">
+        <v>440</v>
+      </c>
+      <c r="I6" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.7">
+      <c r="B7" t="s">
+        <v>470</v>
+      </c>
+      <c r="C7" t="s">
+        <v>440</v>
+      </c>
+      <c r="D7" t="s">
+        <v>440</v>
+      </c>
+      <c r="E7" t="s">
+        <v>440</v>
+      </c>
+      <c r="F7" t="s">
+        <v>440</v>
+      </c>
+      <c r="G7" t="s">
+        <v>440</v>
+      </c>
+      <c r="H7" t="s">
+        <v>440</v>
+      </c>
+      <c r="I7" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.7">
+      <c r="B8" t="s">
+        <v>483</v>
+      </c>
+      <c r="C8" t="s">
+        <v>440</v>
+      </c>
+      <c r="D8" t="s">
+        <v>440</v>
+      </c>
+      <c r="E8" t="s">
+        <v>440</v>
+      </c>
+      <c r="F8" t="s">
+        <v>440</v>
+      </c>
+      <c r="G8" t="s">
+        <v>440</v>
+      </c>
+      <c r="H8" t="s">
+        <v>440</v>
+      </c>
+      <c r="I8" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.7">
+      <c r="B9" t="s">
+        <v>471</v>
+      </c>
+      <c r="C9" t="s">
+        <v>440</v>
+      </c>
+      <c r="D9" t="s">
+        <v>440</v>
+      </c>
+      <c r="E9" t="s">
+        <v>440</v>
+      </c>
+      <c r="F9" t="s">
+        <v>440</v>
+      </c>
+      <c r="G9" t="s">
+        <v>440</v>
+      </c>
+      <c r="H9" t="s">
+        <v>440</v>
+      </c>
+      <c r="I9" t="s">
+        <v>440</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94C427FE-4FBE-4E72-B82C-3613844698B3}">
   <dimension ref="A2:K11"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
@@ -7428,7 +7731,7 @@
       <c r="K5" s="41"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.7">
-      <c r="B6" s="41" t="s">
+      <c r="B6" t="s">
         <v>466</v>
       </c>
       <c r="F6" t="s">
@@ -7446,7 +7749,7 @@
       <c r="K7" s="41"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.7">
-      <c r="B8" s="41" t="s">
+      <c r="B8" t="s">
         <v>465</v>
       </c>
       <c r="H8" t="s">
@@ -7455,13 +7758,13 @@
       <c r="K8" s="41"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.7">
-      <c r="B9" t="s">
+      <c r="B9" s="37" t="s">
         <v>461</v>
       </c>
       <c r="I9" t="s">
         <v>464</v>
       </c>
-      <c r="K9" s="41"/>
+      <c r="K9" s="37"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.7">
       <c r="B10" t="s">
@@ -7495,7 +7798,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37B91805-B5B4-49AB-9E11-D058FB1F0566}">
   <dimension ref="A1:H166"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
